--- a/Result/profitability/8059.xlsx
+++ b/Result/profitability/8059.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.42375</v>
+        <v>-0.45</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.37125</v>
+        <v>-1.4925</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2400000000000002</v>
+        <v>10.25</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>-0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.185</v>
+        <v>-0.18</v>
       </c>
       <c r="N4" t="n">
-        <v>10.43625</v>
+        <v>14.74375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09375000000000003</v>
+        <v>0.009999999999999992</v>
       </c>
       <c r="N5" t="n">
-        <v>14.98875</v>
+        <v>15.78</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16125</v>
+        <v>0.155</v>
       </c>
       <c r="N6" t="n">
-        <v>17.6175</v>
+        <v>17.8375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>0.355</v>
+        <v>0.28625</v>
       </c>
       <c r="N7" t="n">
-        <v>19.5875</v>
+        <v>19.44375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.37875</v>
+        <v>0.32125</v>
       </c>
       <c r="N8" t="n">
-        <v>21.24625</v>
+        <v>20.49125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4062499999999999</v>
+        <v>0.40625</v>
       </c>
       <c r="N9" t="n">
         <v>22.18875</v>
@@ -1772,7 +1772,7 @@
         <v>-0.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2475</v>
+        <v>0.2475000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>19.82</v>
@@ -9715,6 +9715,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8059</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2767</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2449</v>
+      </c>
+      <c r="E74" t="n">
+        <v>318</v>
+      </c>
+      <c r="F74" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-35</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-60</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-62</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.5700000000000001</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-9.81875</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="X74" t="n">
+        <v>6.571428571428571</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-6.040000000000001</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.3445521962350258</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-0.6102941176470589</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.226744186046512</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
